--- a/AAII_Financials/Yearly/AM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>AM</t>
   </si>
@@ -656,89 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1041800</v>
+      </c>
+      <c r="E8" s="3">
         <v>920000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>898200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>900700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>792600</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
@@ -754,15 +757,18 @@
       <c r="M8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -799,12 +805,15 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>800</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -841,12 +850,15 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>-400</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,26 +962,29 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3700</v>
+        <v>1000</v>
       </c>
       <c r="E14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F14" s="3">
         <v>26800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>673600</v>
       </c>
-      <c r="G14" s="3">
-        <v>762000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>770000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -982,33 +1001,36 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E15" s="3">
         <v>131800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>108800</v>
       </c>
       <c r="F15" s="3">
         <v>108800</v>
       </c>
       <c r="G15" s="3">
+        <v>108800</v>
+      </c>
+      <c r="H15" s="3">
         <v>95500</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1024,15 +1046,18 @@
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>1000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,37 +1071,38 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>429900</v>
+      </c>
+      <c r="E17" s="3">
         <v>380500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>364600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1018400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1191100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>43900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>8</v>
@@ -1084,30 +1110,33 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>611900</v>
+      </c>
+      <c r="E18" s="3">
         <v>539500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>533600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-117600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-398500</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1126,12 +1155,15 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,26 +1180,27 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E20" s="3">
         <v>94200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>90500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>86400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-59100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1186,30 +1219,33 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>924000</v>
+      </c>
+      <c r="E21" s="3">
         <v>836100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>803500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>148300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-305000</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1225,30 +1261,33 @@
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
+      <c r="N21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>217200</v>
+      </c>
+      <c r="E22" s="3">
         <v>189900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>175300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>147000</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1264,8 +1303,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1273,93 +1312,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500100</v>
+      </c>
+      <c r="E23" s="3">
         <v>443700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>448700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-178200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-457600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>98900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>28600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E24" s="3">
         <v>117500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>117100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-55700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-102500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>32300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>371800</v>
+      </c>
+      <c r="E26" s="3">
         <v>326200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>331600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-122500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-355100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>66600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>371200</v>
+      </c>
+      <c r="E27" s="3">
         <v>325700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>331100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-123100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-355600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>61400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,27 +1717,30 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-105500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-94200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-90500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-86400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>59100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
@@ -1690,54 +1759,60 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>371200</v>
+      </c>
+      <c r="E33" s="3">
         <v>325700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>331100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-123100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-355600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>61400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>371200</v>
+      </c>
+      <c r="E35" s="3">
         <v>325700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>331100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-123100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-355600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>61400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
+      <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1986,38 +2075,41 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E43" s="3">
         <v>87700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>91800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>105600</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
+      <c r="L43" s="3">
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
@@ -2025,12 +2117,15 @@
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,30 +2165,33 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2112,81 +2210,87 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E46" s="3">
         <v>89000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>83800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>93900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>108600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>626600</v>
+      </c>
+      <c r="E47" s="3">
         <v>652800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>696000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>722500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>709600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>23800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2196,27 +2300,30 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3793500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3751400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3394700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3254000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3273400</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2232,33 +2339,36 @@
       <c r="M48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>31700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1215400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1286100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1356800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1427400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2073600</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2274,15 +2384,18 @@
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,30 +2480,33 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E52" s="3">
         <v>12000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>113000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>117700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2403,12 +2522,15 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5737600</v>
+      </c>
+      <c r="E54" s="3">
         <v>5791300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5544000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5610900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6282900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P54" s="3">
         <v>31800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,29 +2656,30 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E57" s="3">
         <v>28300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
@@ -2565,12 +2695,15 @@
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2610,111 +2743,120 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E59" s="3">
         <v>73800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>85500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>80600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>232300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E60" s="3">
         <v>102100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>114000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>94000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>242100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3213200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3361300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3122900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3091600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2892200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2734,41 +2876,44 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>276300</v>
+      </c>
+      <c r="E62" s="3">
         <v>135600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3585900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3599000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3257300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3192600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3139500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>500</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P66" s="3">
         <v>2800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,27 +3302,30 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E72" s="3">
         <v>82800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-132500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-464100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-341600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3168,15 +3341,18 @@
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
+      <c r="N72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O72" s="3">
         <v>0</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2151700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2192300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2286700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2418300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3143400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>30900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P76" s="3">
         <v>29000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O80" s="2">
+      <c r="O80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>371200</v>
+      </c>
+      <c r="E81" s="3">
         <v>325700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>331100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-123100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-355600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>61400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,26 +3689,27 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>206700</v>
+      </c>
+      <c r="E83" s="3">
         <v>202400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>179500</v>
       </c>
       <c r="F83" s="3">
         <v>179500</v>
       </c>
       <c r="G83" s="3">
+        <v>179500</v>
+      </c>
+      <c r="H83" s="3">
         <v>152500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3527,15 +3725,18 @@
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>779100</v>
+      </c>
+      <c r="E89" s="3">
         <v>699600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>709800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>753400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>622400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>83500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,26 +4023,27 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-184000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-515700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-232800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-196700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-393000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
@@ -3839,15 +4059,18 @@
       <c r="M91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-15800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,27 +4155,30 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-183200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-493800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-233200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-219200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-525700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
@@ -3965,15 +4194,18 @@
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-15800</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,32 +4222,33 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-435400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-433400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-471700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-590200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-496200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-86500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-31700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,51 +4399,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-595800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-205800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-477200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-534700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-98300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-86700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-31700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>16400</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4241,49 +4489,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>-600</v>
       </c>
       <c r="G102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>AM</t>
   </si>
@@ -728,19 +728,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1041800</v>
+        <v>1112400</v>
       </c>
       <c r="E8" s="3">
-        <v>920000</v>
+        <v>990700</v>
       </c>
       <c r="F8" s="3">
-        <v>898200</v>
+        <v>968900</v>
       </c>
       <c r="G8" s="3">
-        <v>900700</v>
+        <v>971400</v>
       </c>
       <c r="H8" s="3">
-        <v>792600</v>
+        <v>849600</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>8</v>
@@ -772,20 +772,20 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>180300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>157100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>165400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>195800</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>8</v>
@@ -817,20 +817,20 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>899300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>810400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>811800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>806000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>653800</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>8</v>
@@ -972,19 +972,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="E14" s="3">
-        <v>4200</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="3">
-        <v>26800</v>
+        <v>30400</v>
       </c>
       <c r="G14" s="3">
-        <v>673600</v>
+        <v>676600</v>
       </c>
       <c r="H14" s="3">
-        <v>770000</v>
+        <v>776000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1031,11 +1031,11 @@
       <c r="H15" s="3">
         <v>95500</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1078,19 +1078,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>429900</v>
+        <v>494400</v>
       </c>
       <c r="E17" s="3">
-        <v>380500</v>
+        <v>449700</v>
       </c>
       <c r="F17" s="3">
-        <v>364600</v>
+        <v>404900</v>
       </c>
       <c r="G17" s="3">
-        <v>1018400</v>
+        <v>412500</v>
       </c>
       <c r="H17" s="3">
-        <v>1191100</v>
+        <v>472100</v>
       </c>
       <c r="I17" s="3">
         <v>43900</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>611900</v>
+        <v>618000</v>
       </c>
       <c r="E18" s="3">
-        <v>539500</v>
+        <v>540900</v>
       </c>
       <c r="F18" s="3">
-        <v>533600</v>
+        <v>564000</v>
       </c>
       <c r="G18" s="3">
-        <v>-117600</v>
+        <v>558900</v>
       </c>
       <c r="H18" s="3">
-        <v>-398500</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>8</v>
+        <v>377500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-41100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>8</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>105500</v>
+        <v>-105500</v>
       </c>
       <c r="E20" s="3">
-        <v>94200</v>
+        <v>-94200</v>
       </c>
       <c r="F20" s="3">
-        <v>90500</v>
+        <v>-90500</v>
       </c>
       <c r="G20" s="3">
-        <v>86400</v>
+        <v>-86400</v>
       </c>
       <c r="H20" s="3">
-        <v>-59100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
+        <v>-51300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-142900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-69700</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>924000</v>
+        <v>859600</v>
       </c>
       <c r="E21" s="3">
-        <v>836100</v>
+        <v>766900</v>
       </c>
       <c r="F21" s="3">
-        <v>803500</v>
+        <v>763200</v>
       </c>
       <c r="G21" s="3">
-        <v>148300</v>
+        <v>754200</v>
       </c>
       <c r="H21" s="3">
-        <v>-305000</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
+        <v>524400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>99100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>28600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1288,11 +1288,11 @@
       <c r="G22" s="3">
         <v>147000</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
+      <c r="H22" s="3">
+        <v>110400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>100</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
@@ -1520,7 +1520,7 @@
         <v>61400</v>
       </c>
       <c r="J27" s="3">
-        <v>2300</v>
+        <v>6500</v>
       </c>
       <c r="K27" s="3">
         <v>9700</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-105500</v>
+        <v>105500</v>
       </c>
       <c r="E32" s="3">
-        <v>-94200</v>
+        <v>94200</v>
       </c>
       <c r="F32" s="3">
-        <v>-90500</v>
+        <v>90500</v>
       </c>
       <c r="G32" s="3">
-        <v>-86400</v>
+        <v>86400</v>
       </c>
       <c r="H32" s="3">
-        <v>59100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
+        <v>51300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>142900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>69700</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
@@ -1772,22 +1772,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>371200</v>
+        <v>371800</v>
       </c>
       <c r="E33" s="3">
-        <v>325700</v>
+        <v>326200</v>
       </c>
       <c r="F33" s="3">
-        <v>331100</v>
+        <v>331600</v>
       </c>
       <c r="G33" s="3">
-        <v>-123100</v>
+        <v>-122500</v>
       </c>
       <c r="H33" s="3">
-        <v>-355600</v>
+        <v>-355100</v>
       </c>
       <c r="I33" s="3">
-        <v>61400</v>
+        <v>66600</v>
       </c>
       <c r="J33" s="3">
         <v>2300</v>
@@ -1862,22 +1862,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>371200</v>
+        <v>371800</v>
       </c>
       <c r="E35" s="3">
-        <v>325700</v>
+        <v>326200</v>
       </c>
       <c r="F35" s="3">
-        <v>331100</v>
+        <v>331600</v>
       </c>
       <c r="G35" s="3">
-        <v>-123100</v>
+        <v>-122500</v>
       </c>
       <c r="H35" s="3">
-        <v>-355600</v>
+        <v>-355100</v>
       </c>
       <c r="I35" s="3">
-        <v>61400</v>
+        <v>66600</v>
       </c>
       <c r="J35" s="3">
         <v>2300</v>
@@ -2000,8 +2000,8 @@
       <c r="E41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G41" s="3">
         <v>600</v>
@@ -2102,8 +2102,8 @@
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>626600</v>
+        <v>626700</v>
       </c>
       <c r="E47" s="3">
         <v>652800</v>
@@ -2369,11 +2369,11 @@
       <c r="H49" s="3">
         <v>2073600</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -2499,13 +2499,13 @@
         <v>12700</v>
       </c>
       <c r="G52" s="3">
-        <v>113000</v>
+        <v>9600</v>
       </c>
       <c r="H52" s="3">
-        <v>117700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1300</v>
+        <v>14500</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15000</v>
+        <v>10500</v>
       </c>
       <c r="E57" s="3">
-        <v>28300</v>
+        <v>22900</v>
       </c>
       <c r="F57" s="3">
-        <v>28500</v>
+        <v>23600</v>
       </c>
       <c r="G57" s="3">
-        <v>13400</v>
+        <v>9500</v>
       </c>
       <c r="H57" s="3">
-        <v>9800</v>
+        <v>6600</v>
       </c>
       <c r="I57" s="3">
-        <v>700</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>81500</v>
+        <v>27500</v>
       </c>
       <c r="E59" s="3">
-        <v>73800</v>
+        <v>23100</v>
       </c>
       <c r="F59" s="3">
-        <v>85500</v>
+        <v>34500</v>
       </c>
       <c r="G59" s="3">
-        <v>80600</v>
+        <v>20900</v>
       </c>
       <c r="H59" s="3">
-        <v>232300</v>
+        <v>158700</v>
       </c>
       <c r="I59" s="3">
-        <v>16100</v>
+        <v>16400</v>
       </c>
       <c r="J59" s="3">
-        <v>14200</v>
+        <v>13900</v>
       </c>
       <c r="K59" s="3">
         <v>7100</v>
@@ -2888,13 +2888,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>276300</v>
+        <v>10400</v>
       </c>
       <c r="E62" s="3">
-        <v>135600</v>
+        <v>4400</v>
       </c>
       <c r="F62" s="3">
-        <v>20400</v>
+        <v>6700</v>
       </c>
       <c r="G62" s="3">
         <v>7000</v>
@@ -3632,22 +3632,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>371200</v>
+        <v>371800</v>
       </c>
       <c r="E81" s="3">
-        <v>325700</v>
+        <v>326200</v>
       </c>
       <c r="F81" s="3">
-        <v>331100</v>
+        <v>331600</v>
       </c>
       <c r="G81" s="3">
-        <v>-123100</v>
+        <v>-122500</v>
       </c>
       <c r="H81" s="3">
-        <v>-355600</v>
+        <v>-355100</v>
       </c>
       <c r="I81" s="3">
-        <v>61400</v>
+        <v>66600</v>
       </c>
       <c r="J81" s="3">
         <v>2300</v>
@@ -3696,19 +3696,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>206700</v>
+        <v>136100</v>
       </c>
       <c r="E83" s="3">
-        <v>202400</v>
+        <v>131800</v>
       </c>
       <c r="F83" s="3">
-        <v>179500</v>
+        <v>108800</v>
       </c>
       <c r="G83" s="3">
-        <v>179500</v>
+        <v>108800</v>
       </c>
       <c r="H83" s="3">
-        <v>152500</v>
+        <v>95500</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
@@ -4042,7 +4042,7 @@
         <v>-196700</v>
       </c>
       <c r="H91" s="3">
-        <v>-393000</v>
+        <v>-392000</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-435400</v>
+        <v>434800</v>
       </c>
       <c r="E96" s="3">
-        <v>-433400</v>
+        <v>432800</v>
       </c>
       <c r="F96" s="3">
-        <v>-471700</v>
+        <v>471200</v>
       </c>
       <c r="G96" s="3">
-        <v>-590200</v>
+        <v>589600</v>
       </c>
       <c r="H96" s="3">
-        <v>-496200</v>
+        <v>495800</v>
       </c>
       <c r="I96" s="3">
-        <v>-86500</v>
+        <v>86500</v>
       </c>
       <c r="J96" s="3">
-        <v>-31700</v>
+        <v>16000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4453,26 +4453,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/AM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>AM</t>
   </si>
@@ -656,95 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1176900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1112400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>990700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>968900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>971400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>849600</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
@@ -760,36 +763,39 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E9" s="3">
         <v>213200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>180300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>157100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>165400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>195800</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
@@ -808,33 +814,36 @@
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>800</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>958900</v>
+      </c>
+      <c r="E10" s="3">
         <v>899300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>810400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>811800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>806000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>653800</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
@@ -853,12 +862,15 @@
       <c r="O10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-400</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,30 +981,33 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E14" s="3">
         <v>6200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>30400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>676600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>776000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1004,41 +1023,44 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E15" s="3">
         <v>136100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>131800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>108800</v>
       </c>
       <c r="G15" s="3">
         <v>108800</v>
       </c>
       <c r="H15" s="3">
+        <v>108800</v>
+      </c>
+      <c r="I15" s="3">
         <v>95500</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1049,15 +1071,18 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,40 +1097,41 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>516600</v>
+      </c>
+      <c r="E17" s="3">
         <v>494400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>449700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>404900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>412500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>472100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>8</v>
@@ -1113,39 +1139,42 @@
       <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>660200</v>
+      </c>
+      <c r="E18" s="3">
         <v>618000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>540900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>564000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>558900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>377500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-43900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1158,12 +1187,15 @@
       <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,35 +1213,36 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-110600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-105500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-94200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-90500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-86400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-51300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-142900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-69700</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1222,39 +1255,42 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>910800</v>
+      </c>
+      <c r="E21" s="3">
         <v>859600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>766900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>763200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>754200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>524400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>99100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1264,39 +1300,42 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
+      <c r="O21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E22" s="3">
         <v>217200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>189900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>175300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>147000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>110400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1306,8 +1345,8 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1315,99 +1354,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>548600</v>
+      </c>
+      <c r="E23" s="3">
         <v>500100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>443700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>448700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-178200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-457600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>98900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>28600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E24" s="3">
         <v>128300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>117500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>117100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-55700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-102500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>32300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E26" s="3">
         <v>371800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>326200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>331600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-122500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-355100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>66600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400300</v>
+      </c>
+      <c r="E27" s="3">
         <v>371200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>325700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>331100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-123100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-355600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>61400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,36 +1786,39 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>110600</v>
+      </c>
+      <c r="E32" s="3">
         <v>105500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>94200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>90500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>86400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>51300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>142900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>69700</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
@@ -1762,57 +1831,63 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E33" s="3">
         <v>371800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>326200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>331600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-122500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-355100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>66600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E35" s="3">
         <v>371800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>326200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>331600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-122500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-355100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>66600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2078,41 +2167,44 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E43" s="3">
         <v>89600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>87700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>82900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>91800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>105600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
@@ -2120,12 +2212,15 @@
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,33 +2263,36 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2213,87 +2311,93 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E46" s="3">
         <v>91100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>89000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>83800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>93900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E47" s="3">
         <v>626700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>652800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>696000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>722500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>709600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>23800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2303,30 +2407,33 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3881600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3793500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3751400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3394700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3254000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3273400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2342,41 +2449,44 @@
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>31700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1144800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1215400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1286100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1356800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1427400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2073600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
@@ -2387,15 +2497,18 @@
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,30 +2599,33 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E52" s="3">
         <v>10900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2525,12 +2644,15 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5761700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5737600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5791300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5544000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5610900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6282900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54" s="3">
         <v>31800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,35 +2786,36 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E57" s="3">
         <v>10500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6600</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
@@ -2698,12 +2828,15 @@
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2746,120 +2879,129 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E59" s="3">
         <v>27500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>158700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E60" s="3">
         <v>96400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>102100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>114000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>94000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>242100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3117000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3213200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3361300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3122900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3091600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2892200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2879,44 +3021,47 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E62" s="3">
         <v>10400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3646600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3585900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3599000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3257300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3192600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3139500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>500</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,30 +3475,33 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E72" s="3">
         <v>100400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-132500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-464100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-341600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3344,15 +3517,18 @@
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
+      <c r="O72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2115200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2151700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2192300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2286700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2418300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3143400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76" s="3">
         <v>29000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P80" s="2">
+      <c r="P80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E81" s="3">
         <v>371800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>326200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>331600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-122500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-355100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>66600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,29 +3887,30 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E83" s="3">
         <v>136100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>131800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>108800</v>
       </c>
       <c r="G83" s="3">
         <v>108800</v>
       </c>
       <c r="H83" s="3">
+        <v>108800</v>
+      </c>
+      <c r="I83" s="3">
         <v>95500</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3728,15 +3926,18 @@
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>844000</v>
+      </c>
+      <c r="E89" s="3">
         <v>779100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>699600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>709800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>753400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>622400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,29 +4243,30 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-242300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-184000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-515700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-232800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-196700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-392000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
@@ -4062,15 +4282,18 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,30 +4384,33 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-242700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-183200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-493800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-233200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-219200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-525700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
@@ -4197,15 +4426,18 @@
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,35 +4455,36 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>437600</v>
+      </c>
+      <c r="E96" s="3">
         <v>434800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>432800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>471200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>589600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>495800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>86500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>16000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,54 +4644,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-601300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-595800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-205800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-477200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-534700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-98300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-86700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-31700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>16400</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4474,8 +4722,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4492,52 +4740,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
         <v>-600</v>
       </c>
       <c r="H102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>AM</t>
   </si>
@@ -656,101 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1259100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1176900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1112400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>990700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>968900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>971400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>849600</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
@@ -766,39 +769,42 @@
       <c r="O8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>231900</v>
+      </c>
+      <c r="E9" s="3">
         <v>218000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>213200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>180300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>157100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>165400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>195800</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
@@ -817,36 +823,39 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>800</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1027200</v>
+      </c>
+      <c r="E10" s="3">
         <v>958900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>899300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>810400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>811800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>806000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>653800</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
@@ -865,12 +874,15 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>-400</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,33 +1000,36 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15100</v>
+        <v>94100</v>
       </c>
       <c r="E14" s="3">
-        <v>6200</v>
+        <v>14400</v>
       </c>
       <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>30400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>676600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>776000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1026,44 +1045,47 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E15" s="3">
         <v>140000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>136100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>131800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>108800</v>
       </c>
       <c r="H15" s="3">
         <v>108800</v>
       </c>
       <c r="I15" s="3">
+        <v>108800</v>
+      </c>
+      <c r="J15" s="3">
         <v>95500</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
@@ -1074,15 +1096,18 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>1000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,43 +1123,44 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>516600</v>
+        <v>526800</v>
       </c>
       <c r="E17" s="3">
-        <v>494400</v>
+        <v>517400</v>
       </c>
       <c r="F17" s="3">
+        <v>500400</v>
+      </c>
+      <c r="G17" s="3">
         <v>449700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>404900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>412500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>472100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>8</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>8</v>
@@ -1142,42 +1168,45 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>660200</v>
+        <v>732300</v>
       </c>
       <c r="E18" s="3">
-        <v>618000</v>
+        <v>659500</v>
       </c>
       <c r="F18" s="3">
+        <v>612000</v>
+      </c>
+      <c r="G18" s="3">
         <v>540900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>564000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>558900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>377500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-43900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-41100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1190,12 +1219,15 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>-1800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,38 +1246,39 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-116400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-110600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-105500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-94200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-90500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-86400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-51300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-142900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-69700</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1258,42 +1291,45 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>910800</v>
+        <v>983000</v>
       </c>
       <c r="E21" s="3">
-        <v>859600</v>
+        <v>910100</v>
       </c>
       <c r="F21" s="3">
+        <v>853500</v>
+      </c>
+      <c r="G21" s="3">
         <v>766900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>763200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>754200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>524400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>99100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>28600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1303,42 +1339,45 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>190400</v>
+      </c>
+      <c r="E22" s="3">
         <v>207000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>217200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>189900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>175300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>147000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>110400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1348,8 +1387,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1357,105 +1396,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>564200</v>
+      </c>
+      <c r="E23" s="3">
         <v>548600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>443700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>448700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-178200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-457600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>98900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E24" s="3">
         <v>147700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>128300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>117500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>117100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-55700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-102500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>413200</v>
+      </c>
+      <c r="E26" s="3">
         <v>400900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>371800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>326200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>331600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-122500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-355100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>66600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>412600</v>
+      </c>
+      <c r="E27" s="3">
         <v>400300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>371200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>325700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>331100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-123100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-355600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>61400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,39 +1855,42 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E32" s="3">
         <v>110600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>105500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>94200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>90500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>86400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>51300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>142900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>69700</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
@@ -1834,60 +1903,66 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>413200</v>
+      </c>
+      <c r="E33" s="3">
         <v>400900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>371800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>326200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>331600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-122500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-355100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>66600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>413200</v>
+      </c>
+      <c r="E35" s="3">
         <v>400900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>371800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>326200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>331600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-122500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-355100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>66600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3">
+        <v>180400</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2170,44 +2259,47 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>109700</v>
+      </c>
+      <c r="E43" s="3">
         <v>116000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>89600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>87700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>82900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>91800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>105600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
@@ -2215,12 +2307,15 @@
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,36 +2361,39 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2314,93 +2412,99 @@
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>379900</v>
+      </c>
+      <c r="E46" s="3">
         <v>118100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>89000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>83800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>93900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>585800</v>
+      </c>
+      <c r="E47" s="3">
         <v>604000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>626700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>652800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>696000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>722500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>709600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>23800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2410,33 +2514,36 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3454600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3881600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3793500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3751400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3394700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3254000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3273400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2452,44 +2559,47 @@
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
         <v>31700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1074100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1144800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1215400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1286100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1356800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1427400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2073600</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
@@ -2500,15 +2610,18 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,33 +2718,36 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>389800</v>
+      </c>
+      <c r="E52" s="3">
         <v>13300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2647,12 +2766,15 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5884100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5761700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5737600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5791300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5544000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5610900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6282900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R54" s="3">
         <v>31800</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,38 +2916,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E57" s="3">
         <v>12300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6600</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
@@ -2831,12 +2961,15 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2882,129 +3015,138 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E59" s="3">
         <v>15700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>158700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E60" s="3">
         <v>100600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>96400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>102100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>114000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>94000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>242100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R60" s="3">
         <v>2700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3222500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3117000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3213200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3361300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3122900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3091600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2892200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3024,47 +3166,50 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E62" s="3">
         <v>15400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3074,9 +3219,12 @@
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3912100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3646600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3585900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3599000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3257300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3192600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3139500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R66" s="3">
         <v>2800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,33 +3648,36 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E72" s="3">
         <v>90500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>100400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>82800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-132500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-464100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-341600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3520,15 +3693,18 @@
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
+      <c r="P72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1972000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2115200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2151700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2192300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2286700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2418300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3143400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R76" s="3">
         <v>29000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>413200</v>
+      </c>
+      <c r="E81" s="3">
         <v>400900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>371800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>326200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>331600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-122500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-355100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>66600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,32 +4085,33 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E83" s="3">
         <v>140000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>136100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>131800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>108800</v>
       </c>
       <c r="H83" s="3">
         <v>108800</v>
       </c>
       <c r="I83" s="3">
+        <v>108800</v>
+      </c>
+      <c r="J83" s="3">
         <v>95500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3929,15 +4127,18 @@
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>1000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>932500</v>
+      </c>
+      <c r="E89" s="3">
         <v>844000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>779100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>699600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>709800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>753400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>622400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>83500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,32 +4463,33 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-162300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-242300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-184000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-515700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-232800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-196700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-392000</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
@@ -4285,15 +4505,18 @@
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-15800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,33 +4613,36 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-169200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-242700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-183200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-493800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-233200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-219200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-525700</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
@@ -4429,15 +4658,18 @@
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-15800</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,38 +4688,39 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E96" s="3">
         <v>437600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>434800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>432800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>471200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>589600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>495800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>86500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>16000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,57 +4889,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-601300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-595800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-205800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-477200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-534700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-98300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-86700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-31700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>16400</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4725,8 +4973,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4743,55 +4991,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-600</v>
       </c>
       <c r="I102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
